--- a/createExcel/workbook.xlsx
+++ b/createExcel/workbook.xlsx
@@ -56,7 +56,7 @@
     <t>ad</t>
   </si>
   <si>
-    <t>1222222222</t>
+    <t>122</t>
   </si>
 </sst>
 </file>

--- a/createExcel/workbook.xlsx
+++ b/createExcel/workbook.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>1111</t>
   </si>
@@ -36,27 +36,6 @@
   </si>
   <si>
     <t>www</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>vs</t>
-  </si>
-  <si>
-    <t>da</t>
-  </si>
-  <si>
-    <t>aa</t>
-  </si>
-  <si>
-    <t>ss</t>
-  </si>
-  <si>
-    <t>ad</t>
-  </si>
-  <si>
-    <t>122</t>
   </si>
 </sst>
 </file>
@@ -101,7 +80,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -130,32 +109,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>14</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
